--- a/Assets/Csv/MusicState.xlsx
+++ b/Assets/Csv/MusicState.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\240627\source\repos\BeatRunner\Assets\Csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE3A24\ゲーム制作\BeatRunner\BeatRunner\Assets\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619A2173-895E-4544-9EE9-3DBD56D27DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41109999-28B3-4373-AFA2-FA006E2603D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2532" yWindow="2484" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="1752" windowWidth="17280" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,10 +42,11 @@
     <t>Chartreuse Green</t>
   </si>
   <si>
+    <t>Dogbite</t>
+  </si>
+  <si>
     <t>Psyched Fevereiro</t>
-  </si>
-  <si>
-    <t>Dogbite</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -404,7 +405,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -415,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>5</v>
